--- a/Table.xlsx
+++ b/Table.xlsx
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.0353</v>
+        <v>0.0389</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.0394</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.0262</v>
+        <v>0.0293</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.0598</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.0266</v>
+        <v>0.0295</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.1691</v>
+        <v>-0.0086</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.1927</v>
+        <v>0.0223</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.189</v>
+        <v>-0.0149</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1458</v>
+        <v>-0.1868</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.167</v>
+        <v>-0.0276</v>
       </c>
     </row>
     <row r="17">
@@ -1293,19 +1293,19 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.0626</v>
+        <v>0.076</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.0524</v>
+        <v>0.065</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0519</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.105</v>
+        <v>0.1692</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.0408</v>
+        <v>0.0555</v>
       </c>
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="2" t="inlineStr">
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.2492</v>
+        <v>-0.1057</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.2798</v>
+        <v>-0.1085</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.5165999999999999</v>
+        <v>-0.0742</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.4161</v>
+        <v>-0.5155</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.3461</v>
+        <v>-0.2047</v>
       </c>
     </row>
     <row r="18">
@@ -1836,38 +1836,38 @@
       </c>
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="n">
-        <v>0.5901</v>
+        <v>0.2391</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.6192</v>
+        <v>0.2682</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.6327</v>
+        <v>0.0554</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.6279</v>
+        <v>0.2245</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.6337</v>
+        <v>0.0496</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n">
-        <v>0.6948</v>
+        <v>0.2099</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.7551</v>
+        <v>0.0379</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.718</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.7733</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="41">
